--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,106 +425,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>County</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Claim_Deadline_Date</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Statute_Citation</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -582,7 +604,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -591,22 +613,32 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>2029-07-01</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -674,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -683,22 +715,32 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>2029-08-12</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>https://www.cobbtax.org/</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -766,7 +808,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -775,22 +817,32 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>2029-07-15</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -802,7 +854,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DeKalb</t>
+          <t>Dekalb</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -858,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -867,22 +919,32 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>2029-08-05</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>https://www.dekalbcountytax.org/</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -950,7 +1012,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -959,22 +1021,32 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>2029-07-22</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>https://www.gwinnetttaxcommissioner.com/</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,100 +441,115 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Parcel_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Claim_Deadline_Date</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Statute_Citation</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Record_Type</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>TYPE</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -553,92 +568,107 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>2024-GA-003810</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>MARCUS &amp; ELEANOR JENKINS</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F2" t="b">
+      <c r="G2" t="b">
         <v>1</v>
       </c>
-      <c r="G2" t="b">
+      <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>1420 PEACHTREE ST NE ATLANTA GA 30309</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>134000</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>26800</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>2024-07-02</t>
         </is>
       </c>
-      <c r="O2" t="n">
-        <v>1006</v>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" t="n">
+        <v>1005</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>2029-07-01</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -655,92 +685,107 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>2024-GA-001550</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>ESTATE OF RAYMOND VAUGHN</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Estate / Deceased</t>
         </is>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>1205 ROSWELL RD MARIETTA GA 30062</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>118000</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>23600</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2024-08-13</t>
         </is>
       </c>
-      <c r="O3" t="n">
-        <v>1048</v>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="n">
+        <v>1047</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2029-08-12</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>https://www.cobbtax.org/</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -757,92 +802,107 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>2024-GA-004120</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>ESTATE OF HAROLD CRAWFORD</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Estate / Deceased</t>
         </is>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>892 CASCADE AVE SW ATLANTA GA 30310</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>96500</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>19300</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="O4" t="n">
-        <v>1020</v>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" t="n">
+        <v>1019</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>2029-07-15</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -859,92 +919,107 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>2024-GA-002490</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>TERRENCE &amp; MONICA BRADLEY</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F5" t="b">
+      <c r="G5" t="b">
         <v>1</v>
       </c>
-      <c r="G5" t="b">
+      <c r="H5" t="b">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>2340 LAVISTA RD DECATUR GA 30033</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>82400</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>16480</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>2024-08-06</t>
         </is>
       </c>
-      <c r="O5" t="n">
-        <v>1041</v>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" t="n">
+        <v>1040</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>2029-08-05</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>https://www.dekalbcountytax.org/</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -961,92 +1036,107 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>2024-GA-001920</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>VICTORIA STRICKLAND</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F6" t="b">
+      <c r="G6" t="b">
         <v>1</v>
       </c>
-      <c r="G6" t="b">
+      <c r="H6" t="b">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>4510 LAWRENCEVILLE HWY LILBURN GA 30047</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>67800</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>13560</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>2024-07-23</t>
         </is>
       </c>
-      <c r="O6" t="n">
-        <v>1027</v>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" t="n">
+        <v>1026</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>2029-07-22</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>https://www.gwinnetttaxcommissioner.com/</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-003810</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/</t>
+          <t>https://www.cobbtax.org/excess-funds?docket=2024-GA-001550</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-004120</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/</t>
+          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/</t>
+          <t>https://www.gwinnetttaxcommissioner.com/excess-funds?docket=2024-GA-001920</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-003810</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/excess-funds?docket=2024-GA-001550</t>
+          <t>https://www.cobbtax.org/</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-004120</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
+          <t>https://www.dekalbcountytax.org/</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/excess-funds?docket=2024-GA-001920</t>
+          <t>https://www.gwinnetttaxcommissioner.com/</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/536/Records-Search-Center?docket=2024-GA-003810</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/</t>
+          <t>https://www.cobbtax.org/property/tax_sale/index.php?docket=2024-GA-001550</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/536/Records-Search-Center?docket=2024-GA-004120</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/</t>
+          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/</t>
+          <t>https://www.gwinnetttaxcommissioner.com/property-tax/tax-sale-excess-funds?docket=2024-GA-001920</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12922,7 +12922,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13582,7 +13582,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14100,7 +14100,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14364,7 +14364,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14496,7 +14496,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14628,7 +14628,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14760,7 +14760,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14892,7 +14892,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15816,7 +15816,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15948,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16080,7 +16080,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16872,7 +16872,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17136,7 +17136,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17664,7 +17664,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17796,7 +17796,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17928,7 +17928,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18060,7 +18060,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18192,7 +18192,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18720,7 +18720,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18852,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12922,7 +12922,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13582,7 +13582,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14100,7 +14100,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14364,7 +14364,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14496,7 +14496,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14628,7 +14628,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14760,7 +14760,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14892,7 +14892,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15816,7 +15816,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15948,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16080,7 +16080,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16872,7 +16872,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17136,7 +17136,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17664,7 +17664,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17796,7 +17796,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17928,7 +17928,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18060,7 +18060,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18192,7 +18192,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18720,7 +18720,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18852,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12922,7 +12922,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13582,7 +13582,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14100,7 +14100,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14364,7 +14364,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14496,7 +14496,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14628,7 +14628,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14760,7 +14760,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14892,7 +14892,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15816,7 +15816,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15948,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16080,7 +16080,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16872,7 +16872,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17136,7 +17136,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17664,7 +17664,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17796,7 +17796,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17928,7 +17928,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18060,7 +18060,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18192,7 +18192,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18720,7 +18720,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18852,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,142 +429,142 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>County</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Parcel_ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Claim_Deadline_Date</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Verify_Note</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Source_URL</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Statute_Citation</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Record_Type</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Retrieved_At</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -627,7 +639,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -681,12 +693,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -759,7 +771,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -813,12 +825,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -891,7 +903,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +957,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1035,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1077,12 +1089,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1167,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1209,12 +1221,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1299,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1341,12 +1353,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1431,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1473,12 +1485,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1563,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1605,12 +1617,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1695,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1737,12 +1749,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1827,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1869,12 +1881,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1959,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2001,12 +2013,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2091,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2133,12 +2145,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2223,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2265,12 +2277,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2355,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2397,12 +2409,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2487,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2529,12 +2541,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2619,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2661,12 +2673,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2751,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2793,12 +2805,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2883,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2925,12 +2937,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3015,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3057,12 +3069,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3147,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3189,12 +3201,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3279,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3321,12 +3333,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3411,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3453,12 +3465,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3543,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3585,12 +3597,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3675,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3717,12 +3729,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3807,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3849,12 +3861,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3939,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3981,12 +3993,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4071,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4113,12 +4125,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4203,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4245,12 +4257,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4335,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4377,12 +4389,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4467,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4509,12 +4521,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4599,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4641,12 +4653,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4731,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4773,12 +4785,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4863,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4905,12 +4917,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4995,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5037,12 +5049,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5127,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5169,12 +5181,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5259,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5301,12 +5313,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5391,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5433,12 +5445,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5523,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5565,12 +5577,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5655,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5697,12 +5709,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5787,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5829,12 +5841,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5919,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5961,12 +5973,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6083,12 +6095,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6173,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6215,12 +6227,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6337,12 +6349,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6427,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6469,12 +6481,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6559,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6601,12 +6613,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6691,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6733,12 +6745,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6823,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6865,12 +6877,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6943,7 +6955,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6997,12 +7009,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7087,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -7129,12 +7141,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7219,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7261,12 +7273,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7351,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7393,12 +7405,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7483,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7525,12 +7537,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7603,7 +7615,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7657,12 +7669,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7735,7 +7747,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7789,12 +7801,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7867,7 +7879,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7921,12 +7933,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7999,7 +8011,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -8053,12 +8065,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8143,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -8185,12 +8197,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8275,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8317,12 +8329,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8407,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8449,12 +8461,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8539,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8581,12 +8593,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8671,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8713,12 +8725,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8803,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8845,12 +8857,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8923,7 +8935,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8977,12 +8989,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9055,7 +9067,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -9109,12 +9121,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9187,7 +9199,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9241,12 +9253,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9331,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9373,12 +9385,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9463,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9505,12 +9517,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9583,7 +9595,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9637,12 +9649,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9727,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9769,12 +9781,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9859,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9901,12 +9913,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9991,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -10033,12 +10045,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10111,7 +10123,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -10165,12 +10177,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10255,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10297,12 +10309,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10375,7 +10387,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10429,12 +10441,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10519,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10561,12 +10573,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10639,7 +10651,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10693,12 +10705,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10771,7 +10783,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10825,12 +10837,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10903,7 +10915,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10957,12 +10969,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11035,7 +11047,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -11089,12 +11101,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11167,7 +11179,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -11221,12 +11233,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11343,12 +11355,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11433,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11475,12 +11487,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11553,7 +11565,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11607,12 +11619,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11729,12 +11741,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11819,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-139</v>
+        <v>-140</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11861,12 +11873,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11939,7 +11951,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11993,12 +12005,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12071,7 +12083,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -12125,12 +12137,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12203,7 +12215,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -12257,12 +12269,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12335,7 +12347,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12389,12 +12401,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12467,7 +12479,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12521,12 +12533,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12611,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12653,12 +12665,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12743,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12785,12 +12797,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12863,7 +12875,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12917,12 +12929,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12995,7 +13007,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -13049,12 +13061,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13127,7 +13139,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -13181,12 +13193,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13259,7 +13271,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -13313,12 +13325,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13403,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13445,12 +13457,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13535,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13577,12 +13589,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13655,7 +13667,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13709,12 +13721,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13787,7 +13799,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13841,12 +13853,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13919,7 +13931,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13973,12 +13985,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14095,12 +14107,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14173,7 +14185,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -14227,12 +14239,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14305,7 +14317,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14359,12 +14371,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14437,7 +14449,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14491,12 +14503,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14569,7 +14581,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14623,12 +14635,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14701,7 +14713,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14755,12 +14767,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14845,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14887,12 +14899,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14965,7 +14977,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -15019,12 +15031,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15097,7 +15109,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -15151,12 +15163,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15241,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -15283,12 +15295,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15361,7 +15373,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -15415,12 +15427,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15493,7 +15505,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15547,12 +15559,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15625,7 +15637,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15679,12 +15691,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15769,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15811,12 +15823,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15889,7 +15901,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15943,12 +15955,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -16021,7 +16033,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -16075,12 +16087,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -16153,7 +16165,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -16207,12 +16219,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -16285,7 +16297,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -16339,12 +16351,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -16417,7 +16429,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -16471,12 +16483,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16561,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16603,12 +16615,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -16681,7 +16693,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16735,12 +16747,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -16813,7 +16825,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16867,12 +16879,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -16945,7 +16957,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16999,12 +17011,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17089,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -17131,12 +17143,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17221,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -17263,12 +17275,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -17341,7 +17353,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -17395,12 +17407,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -17473,7 +17485,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17527,12 +17539,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -17605,7 +17617,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17659,12 +17671,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17749,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17791,12 +17803,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -17869,7 +17881,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17923,12 +17935,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -18001,7 +18013,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -18055,12 +18067,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -18133,7 +18145,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -18187,12 +18199,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -18265,7 +18277,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -18319,12 +18331,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -18397,7 +18409,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -18451,12 +18463,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -18529,7 +18541,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18583,12 +18595,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -18661,7 +18673,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18715,12 +18727,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -18793,7 +18805,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18847,12 +18859,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -586,11 +586,7 @@
           <t>R7233 032</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>GW-R7233-032</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>SAMIYA MUSTAFA</t>
@@ -639,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -693,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -718,11 +714,7 @@
           <t>R7088 348</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>GW-R7088-348</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>DAVIDSON TAWANA L</t>
@@ -771,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -825,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -850,11 +842,7 @@
           <t>R7026 283</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>GW-R7026-283</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>MINTON EVELYN TICE</t>
@@ -903,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -957,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -982,11 +970,7 @@
           <t>18 158 09 007</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>DK-18-158-09-007</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>DENNIS N HAROLD ESTATE</t>
@@ -1035,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1089,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1114,11 +1098,7 @@
           <t>18 319 05 030</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>DK-18-319-05-030</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>PATTI MURR CARRERAS</t>
@@ -1167,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1221,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1246,11 +1226,7 @@
           <t>R6226 086</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>GW-R6226-086</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>RIDING WILLIAM S &amp; KIMA S</t>
@@ -1299,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1353,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1378,11 +1354,7 @@
           <t>18 099 04 011</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>DK-18-099-04-011</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>WILLIAM H ALSABROOK ESTATE</t>
@@ -1431,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1485,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1510,11 +1482,7 @@
           <t>18 106 13 058</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>DK-18-106-13-058</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>DAVID E. AND MARK H SCHMITT</t>
@@ -1563,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1617,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1642,11 +1610,7 @@
           <t>18 299 19 133</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>DK-18-299-19-133</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>PASHA CONNELL</t>
@@ -1695,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1749,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1774,11 +1738,7 @@
           <t>18 015 06 061</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>DK-18-015-06-061</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>ELIZABETH BIZUNCH</t>
@@ -1827,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1881,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1906,11 +1866,7 @@
           <t>18 297 08 001</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>DK-18-297-08-001</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>ANNE PETTIGREW ESTATE</t>
@@ -1959,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2013,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2038,11 +1994,7 @@
           <t>R6180D017</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>GW-R6180D017</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>CAMERON ROBERT ALANSON ETAL</t>
@@ -2091,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2145,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2170,11 +2122,7 @@
           <t>18 038 07 016</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>DK-18-038-07-016</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>GILBERTO MACHADO</t>
@@ -2223,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2277,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2302,11 +2250,7 @@
           <t>16 030 02 025</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>DK-16-030-02-025</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>VALERIE ELLISON ESTATE</t>
@@ -2355,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2409,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2434,11 +2378,7 @@
           <t>16 061 12 023</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>DK-16-061-12-023</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>DEBORAH SOLTAU</t>
@@ -2487,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2541,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2566,11 +2506,7 @@
           <t>16 130 01 010</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>DK-16-130-01-010</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>REESE GEORGE W EST PERS REP AND HEIRS REESE</t>
@@ -2619,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2673,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2698,11 +2634,7 @@
           <t>15 139 05 011</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>DK-15-139-05-011</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>RALPH D DAVIS ESTATE</t>
@@ -2751,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2805,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2830,11 +2762,7 @@
           <t>18 291 08 054</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>DK-18-291-08-054</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>NANCY JEAN BREWER</t>
@@ -2883,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2937,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2962,11 +2890,7 @@
           <t>18 141 15 003</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>DK-18-141-15-003</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>LAURA A HONTGAS REVOCABLE LIVING TRUST HONTGAS</t>
@@ -3015,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3069,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3094,11 +3018,7 @@
           <t>15 062 03 011</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>DK-15-062-03-011</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>EDWARD A MCDONNELL ESTATE</t>
@@ -3147,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3201,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3226,11 +3146,7 @@
           <t>15 163 03 014</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>DK-15-163-03-014</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>HUGH L RUTLEDGE &amp; JAMES K RUTLEDGE ESTATE</t>
@@ -3279,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3333,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3358,11 +3274,7 @@
           <t>16 104 06 040</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>DK-16-104-06-040</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>ABOGHANIM ABDURRHMAN ABDULLAH ABOGHANIM</t>
@@ -3411,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3465,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3490,11 +3402,7 @@
           <t>16 104 08 040</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>DK-16-104-08-040</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>DENISE JENKINS</t>
@@ -3543,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3597,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3622,11 +3530,7 @@
           <t>15 177 04 068</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>DK-15-177-04-068</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>CHARLOTTE B ZOTTI ESTATE</t>
@@ -3675,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3729,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3754,11 +3658,7 @@
           <t>15 132 03 027</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>DK-15-132-03-027</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>DEBBIE PACE</t>
@@ -3807,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3861,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3886,11 +3786,7 @@
           <t>15 184 03 019</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>DK-15-184-03-019</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>LAVERNE OXENDINE JORDAN ESTATE</t>
@@ -3939,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3993,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4018,11 +3914,7 @@
           <t>R6246B123</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>GW-R6246B123</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>IRENE GUTIERREZ</t>
@@ -4071,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4125,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4150,11 +4042,7 @@
           <t>16 002 05 045</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>DK-16-002-05-045</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>REBECCA DARLENE STEPHENS</t>
@@ -4203,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4257,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4282,11 +4170,7 @@
           <t>15 253 04 031</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>DK-15-253-04-031</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>WALTER V LUBOVICK ESTATE</t>
@@ -4335,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4389,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4414,11 +4298,7 @@
           <t>15 089 05 008</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>DK-15-089-05-008</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>HAMID BRICHI</t>
@@ -4467,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4521,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4546,11 +4426,7 @@
           <t>16 153 13 016</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>DK-16-153-13-016</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>JERRY DOBBINS &amp; WANDA DOBBINS</t>
@@ -4599,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4653,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4678,11 +4554,7 @@
           <t>16 075 04 034</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>DK-16-075-04-034</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>MAXIME AND ALICE PAPILLON</t>
@@ -4731,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4785,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4810,11 +4682,7 @@
           <t>16 001 12 003</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>DK-16-001-12-003</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>DENISE A BREDEN</t>
@@ -4863,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4917,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4942,11 +4810,7 @@
           <t>18 092 08 025</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>DK-18-092-08-025</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>DOROTHY JANE WITHERS</t>
@@ -4995,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5049,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5074,11 +4938,7 @@
           <t>18 044 09 034</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>DK-18-044-09-034</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>ALVIN B MARBLE</t>
@@ -5127,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5181,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5206,11 +5066,7 @@
           <t>15 208 04 156</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>DK-15-208-04-156</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>GRAHAM HAY</t>
@@ -5259,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5313,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5338,11 +5194,7 @@
           <t>18 172 01 104</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>DK-18-172-01-104</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>TOP DESIGNS GROUP</t>
@@ -5391,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5445,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5470,11 +5322,7 @@
           <t>18 074 05 019</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>DK-18-074-05-019</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>MYRTIS E PRUITT ESTATE</t>
@@ -5523,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5577,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5602,11 +5450,7 @@
           <t>16 152 04 001</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>DK-16-152-04-001</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>SHANIQUA CAULDWELL</t>
@@ -5655,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5709,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5734,11 +5578,7 @@
           <t>16 074 16 006</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>DK-16-074-16-006</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>BEATRICE ANDREWS</t>
@@ -5787,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5841,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5866,11 +5706,7 @@
           <t>16 154 06 001</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>DK-16-154-06-001</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>ROBERT ODELL HINES ESTATE &amp; LILLIE MAE BENNETT ESTATE</t>
@@ -5919,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5973,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5998,11 +5834,7 @@
           <t>R7044 075</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>GW-R7044-075</t>
-        </is>
-      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>HAYES TIMOTHY L</t>
@@ -6095,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6120,11 +5952,7 @@
           <t>16 123 05 045</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>DK-16-123-05-045</t>
-        </is>
-      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>STELLA M TAYLOR ESTATE</t>
@@ -6173,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6227,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6252,11 +6080,7 @@
           <t>R6321A014</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>GW-R6321A014</t>
-        </is>
-      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>HOLCOMBE MARLON</t>
@@ -6349,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6374,11 +6198,7 @@
           <t>15 220 09 014</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>DK-15-220-09-014</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>BRETT MULLINS</t>
@@ -6427,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6481,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6506,11 +6326,7 @@
           <t>16 009 02 036</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>DK-16-009-02-036</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>BOYD BROOKS &amp; LAKEMBA WARD</t>
@@ -6559,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6613,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6638,11 +6454,7 @@
           <t>R7259 221</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>GW-R7259-221</t>
-        </is>
-      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>LAND BUFORD HWY</t>
@@ -6691,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6745,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6770,11 +6582,7 @@
           <t>R7252 031</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>GW-R7252-031</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>PEACHTREE/SUWANEE</t>
@@ -6823,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6877,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6902,11 +6710,7 @@
           <t>15 229 05 019</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>DK-15-229-05-019</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>CATALINA</t>
@@ -6955,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7009,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7034,11 +6838,7 @@
           <t>R7093 009A</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>GW-R7093-009A</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>SUNNY HILL HOME DEMON</t>
@@ -7087,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -7141,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7166,11 +6966,7 @@
           <t>18 013 06 001</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>DK-18-013-06-001</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>OSCAR O HERNANDEZ PADILLA</t>
@@ -7219,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7273,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7298,11 +7094,7 @@
           <t>R6154 562</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>GW-R6154-562</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>OAKTREE</t>
@@ -7351,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7405,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7430,11 +7222,7 @@
           <t>16 153 08 047</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>DK-16-153-08-047</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>BRENDA PHILPOT</t>
@@ -7483,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7537,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7562,11 +7350,7 @@
           <t>18 309 07 038</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>DK-18-309-07-038</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>NICK LONG JR ESTATE</t>
@@ -7615,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7669,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7694,11 +7478,7 @@
           <t>16 074 07 024</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>DK-16-074-07-024</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>BRETT O MULLINGS</t>
@@ -7747,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7801,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7826,11 +7606,7 @@
           <t>16 074 08 085</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>DK-16-074-08-085</t>
-        </is>
-      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>NATHAN SMITH &amp; STEVEN HAMMOND &amp; DELITA D. PERRINO</t>
@@ -7879,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7933,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7958,11 +7734,7 @@
           <t>15 090 06 039</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>DK-15-090-06-039</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>DREAM ILLUMINATION FOUNDATION</t>
@@ -8011,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -8065,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8090,11 +7862,7 @@
           <t>16 152 11 020</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>DK-16-152-11-020</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>CALVIN CHAN</t>
@@ -8143,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -8197,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8222,11 +7990,7 @@
           <t>16 074 08 083</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>DK-16-074-08-083</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>NATHAN SMITH &amp; STEVEN HAMMOND &amp; LIANE TRUELL</t>
@@ -8275,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8329,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8354,11 +8118,7 @@
           <t>16 141 02 013</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>DK-16-141-02-013</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>DONOVAN SQUIRES</t>
@@ -8407,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8461,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8486,11 +8246,7 @@
           <t>16 074 08 095</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>DK-16-074-08-095</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>NATHAN SMITH &amp; MARY ELIZABETH HIRSCH</t>
@@ -8539,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8593,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8618,11 +8374,7 @@
           <t>15 193 04 026</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>DK-15-193-04-026</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>AKIM RAVARIERE &amp; MELINA RAVARIERE</t>
@@ -8671,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8725,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8750,11 +8502,7 @@
           <t>15 181 05 018</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>DK-15-181-05-018</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>ZION TASHKENT TASHKENT</t>
@@ -8803,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8857,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8882,11 +8630,7 @@
           <t>15 101 01 005</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>DK-15-101-01-005</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>STEVEN EDWARD BRIEN</t>
@@ -8935,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8989,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9014,11 +8758,7 @@
           <t>18 224 01 020</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>DK-18-224-01-020</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>NOAH DOSS</t>
@@ -9067,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -9121,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9146,11 +8886,7 @@
           <t>18 046 03 070</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-070</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>MOSELY FREDRICK HIS ESTATE PERS REP AND HEIRS KNOWN AND UNKNOWN</t>
@@ -9199,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9253,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9278,11 +9014,7 @@
           <t>16 153 08 006</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>DK-16-153-08-006</t>
-        </is>
-      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>RHONEIA N STARKS</t>
@@ -9331,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9385,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9410,11 +9142,7 @@
           <t>15 093 07 006</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>DK-15-093-07-006</t>
-        </is>
-      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>U S HOUSING &amp; URBAN DEV</t>
@@ -9463,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9517,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9542,11 +9270,7 @@
           <t>18 341 10 001</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>DK-18-341-10-001</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>DAVID CHESTNUT</t>
@@ -9595,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9649,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9674,11 +9398,7 @@
           <t>16 074 08 092</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>DK-16-074-08-092</t>
-        </is>
-      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>PATRICIA ANN MARSHALL</t>
@@ -9727,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9781,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9806,11 +9526,7 @@
           <t>R5005 149</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>GW-R5005-149</t>
-        </is>
-      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>WEIDLICH</t>
@@ -9859,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9913,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9938,11 +9654,7 @@
           <t>16 074 07 016</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>DK-16-074-07-016</t>
-        </is>
-      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>TOSHA DEACON</t>
@@ -9991,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -10045,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10070,11 +9782,7 @@
           <t>R7266 232</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>GW-R7266-232</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>ARONSON</t>
@@ -10123,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -10177,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10202,11 +9910,7 @@
           <t>R4346A168</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>GW-R4346A168</t>
-        </is>
-      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>DENSON</t>
@@ -10255,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10309,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10334,11 +10038,7 @@
           <t>18 046 03 087</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-087</t>
-        </is>
-      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>SCOTT JOHN GILBERT</t>
@@ -10387,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10441,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10466,11 +10166,7 @@
           <t>15 090 07 013</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>DK-15-090-07-013</t>
-        </is>
-      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>RODRIGUEZ MARTA GRANDA LIVING RODRIGUEZ MARTA G</t>
@@ -10519,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10573,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10598,11 +10294,7 @@
           <t>R7305 083</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>GW-R7305-083</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>GARMON EVERETT E ETAL</t>
@@ -10651,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10705,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10730,11 +10422,7 @@
           <t>R6058 137</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>GW-R6058-137</t>
-        </is>
-      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>JERE M.</t>
@@ -10783,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10837,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10862,11 +10550,7 @@
           <t>R6281 018</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>GW-R6281-018</t>
-        </is>
-      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>BAY COLONY PROPERTY CO JONES MILL RD</t>
@@ -10915,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10969,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10994,11 +10678,7 @@
           <t>18 126 15 012</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>DK-18-126-15-012</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>ROSA REID ESTATE</t>
@@ -11047,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -11101,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11126,11 +10806,7 @@
           <t>18 015 06 013</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>DK-18-015-06-013</t>
-        </is>
-      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>A AND A INVESTMENT AND</t>
@@ -11179,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -11233,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11258,11 +10934,7 @@
           <t>R6109 102</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>GW-R6109-102</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>COOK</t>
@@ -11355,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11380,11 +11052,7 @@
           <t>R6095 088</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>GW-R6095-088</t>
-        </is>
-      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>CRUSSELLE</t>
@@ -11433,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11487,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11512,11 +11180,7 @@
           <t>15 192 02 010</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>DK-15-192-02-010</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>ELVIA PELAYO</t>
@@ -11565,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11619,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11644,11 +11308,7 @@
           <t>R4346A247</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>GW-R4346A247</t>
-        </is>
-      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>BENJAMIN</t>
@@ -11741,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11766,11 +11426,7 @@
           <t>16 046 01 098</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>DK-16-046-01-098</t>
-        </is>
-      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>ANNMARIE PLUMMER-BAILEY</t>
@@ -11819,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-140</v>
+        <v>-141</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11873,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11898,11 +11554,7 @@
           <t>18 068 11 027</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>DK-18-068-11-027</t>
-        </is>
-      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>ABDULKADIR AHMED</t>
@@ -11951,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -12005,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12030,11 +11682,7 @@
           <t>R4348A062</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>GW-R4348A062</t>
-        </is>
-      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>MARY</t>
@@ -12083,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -12137,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12162,11 +11810,7 @@
           <t>16 218 03 082</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>DK-16-218-03-082</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>MICHAEL BOWMAN</t>
@@ -12215,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -12269,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12294,11 +11938,7 @@
           <t>18 047 23 022</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>DK-18-047-23-022</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>MARY ANN EDWARDS ESTATE</t>
@@ -12347,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12401,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12426,11 +12066,7 @@
           <t>R6067 098</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>GW-R6067-098</t>
-        </is>
-      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>BUTSCH</t>
@@ -12479,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12533,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12558,11 +12194,7 @@
           <t>18 044 09 059</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>DK-18-044-09-059</t>
-        </is>
-      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>JIMMY L JACKSON &amp; MABLE MCWHORTER JACKSON</t>
@@ -12611,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12665,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12690,11 +12322,7 @@
           <t>15 096 02 121</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>DK-15-096-02-121</t>
-        </is>
-      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>CECIL DAVIS ESTATE</t>
@@ -12743,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12797,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12822,11 +12450,7 @@
           <t>15 027 01 090</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>DK-15-027-01-090</t>
-        </is>
-      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>RIVER MILL ROCK MILL CLUB MILL</t>
@@ -12875,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12929,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12954,11 +12578,7 @@
           <t>18 044 09 080</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>DK-18-044-09-080</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>CHARLES E ANDERSON ESTATE</t>
@@ -13007,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -13061,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13086,11 +12706,7 @@
           <t>18 073 01 161</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>DK-18-073-01-161</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>SABRINA YOUNG</t>
@@ -13139,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -13193,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13218,11 +12834,7 @@
           <t>18 004 17 061</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>DK-18-004-17-061</t>
-        </is>
-      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>HOWARD TOMMY EUGENE HOWARD MARY LEE</t>
@@ -13271,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -13325,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13350,11 +12962,7 @@
           <t>R6276 022</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>GW-R6276-022</t>
-        </is>
-      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>BAY COLONY PROPERTY CO JONES MILL CT</t>
@@ -13403,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13457,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13482,11 +13090,7 @@
           <t>15 156 03 001</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>DK-15-156-03-001</t>
-        </is>
-      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>YARED BEEWKETU KASEG</t>
@@ -13535,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13589,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13614,11 +13218,7 @@
           <t>18 225 02 003</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>DK-18-225-02-003</t>
-        </is>
-      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>CHANEREE THIEN</t>
@@ -13667,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13721,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13746,11 +13346,7 @@
           <t>R6128 123</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>GW-R6128-123</t>
-        </is>
-      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>BRENTWOOD-GLOSTER</t>
@@ -13799,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13853,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13878,11 +13474,7 @@
           <t>16 074 14 029</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>DK-16-074-14-029</t>
-        </is>
-      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>JERMAINE PREDESTIN &amp; REGINA MENDEZ</t>
@@ -13931,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13985,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14010,11 +13602,7 @@
           <t>R5140 189</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>GW-R5140-189</t>
-        </is>
-      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>SIBLEY</t>
@@ -14107,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14132,11 +13720,7 @@
           <t>18 187 01 246</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>DK-18-187-01-246</t>
-        </is>
-      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>C.O. EDWARDS &amp; CARL M. CAIN</t>
@@ -14185,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -14239,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14264,11 +13848,7 @@
           <t>16 137 08 011</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>DK-16-137-08-011</t>
-        </is>
-      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>NANCY L KENNEDY</t>
@@ -14317,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14371,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14396,11 +13976,7 @@
           <t>18 046 03 106</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-106</t>
-        </is>
-      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>CRONAN BROTHERS</t>
@@ -14449,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14503,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14528,11 +14104,7 @@
           <t>R4348A061</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>GW-R4348A061</t>
-        </is>
-      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>MARY</t>
@@ -14581,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14635,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14660,11 +14232,7 @@
           <t>16 043 03 078</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>DK-16-043-03-078</t>
-        </is>
-      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>WILLIAM H ROBINSON JR ESTATE</t>
@@ -14713,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14767,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14792,11 +14360,7 @@
           <t>18 046 03 060</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-060</t>
-        </is>
-      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>GWENDOLYN HEATH ESTATE</t>
@@ -14845,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14899,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14924,11 +14488,7 @@
           <t>18 018 01 121</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>DK-18-018-01-121</t>
-        </is>
-      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>MONICA BOBB BOWMAN</t>
@@ -14977,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -15031,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15056,11 +14616,7 @@
           <t>18 046 03 093</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-093</t>
-        </is>
-      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>UNKNOWN OWNER - UNRETURNED PROPERTY</t>
@@ -15109,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -15163,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15188,11 +14744,7 @@
           <t>18 046 03 051</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-051</t>
-        </is>
-      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>ALICE WATKINS</t>
@@ -15241,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -15295,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15320,11 +14872,7 @@
           <t>18 046 03 211</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-211</t>
-        </is>
-      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>BOYD MARIE HER ESTATE ADMINISTRATOR EXECUTOR AND HEIRS KNOWN AND UNKNOWN</t>
@@ -15373,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -15427,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15452,11 +15000,7 @@
           <t>18 046 03 069</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-069</t>
-        </is>
-      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>MARY M MATTHEWS</t>
@@ -15505,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15559,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15584,11 +15128,7 @@
           <t>16 140 02 012</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>DK-16-140-02-012</t>
-        </is>
-      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>WILLIAM H. BROOKS ESTATE</t>
@@ -15637,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15691,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15716,11 +15256,7 @@
           <t>18 046 03 037</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-037</t>
-        </is>
-      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>JAMES GRESHAM</t>
@@ -15769,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15823,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15848,11 +15384,7 @@
           <t>18 046 03 236</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-236</t>
-        </is>
-      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>GALLOWAY JAMES ESTATE PERS REP AND HEIRS KNOWN AND UNKNOWN</t>
@@ -15901,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15955,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15980,11 +15512,7 @@
           <t>18 047 26 017</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>DK-18-047-26-017</t>
-        </is>
-      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>MARY EMILY &amp; SURVARIA BREWER ESTATES</t>
@@ -16033,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -16087,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16112,11 +15640,7 @@
           <t>R6154 569</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>GW-R6154-569</t>
-        </is>
-      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>OAKTREE</t>
@@ -16165,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -16219,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16244,11 +15768,7 @@
           <t>R6183 166</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>GW-R6183-166</t>
-        </is>
-      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>HICKORY</t>
@@ -16297,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -16351,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16376,11 +15896,7 @@
           <t>15 199 04 193</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>DK-15-199-04-193</t>
-        </is>
-      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>GETHSEMANE TEMPLE AFFILIATED WITH UHC</t>
@@ -16429,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -16483,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16508,11 +16024,7 @@
           <t>18 203 06 069</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>DK-18-203-06-069</t>
-        </is>
-      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>MCJENKIN ESTHER H MRS</t>
@@ -16561,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16615,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16640,11 +16152,7 @@
           <t>18 046 03 067</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-067</t>
-        </is>
-      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>UNKNOWN OWNER - UNRETURNED PROPERTY 3180 altacrest dr SCOTTDALE 30079</t>
@@ -16693,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16747,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16772,11 +16280,7 @@
           <t>18 081 05 073</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>DK-18-081-05-073</t>
-        </is>
-      </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>ANNMARIE PLUMMER BAILEY &amp; WINSTON BAILEY</t>
@@ -16825,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16879,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16904,11 +16408,7 @@
           <t>R7069 420</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>GW-R7069-420</t>
-        </is>
-      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>STERLING</t>
@@ -16957,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -17011,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17036,11 +16536,7 @@
           <t>15 122 06 066</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>DK-15-122-06-066</t>
-        </is>
-      </c>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>EDGAR DUNCAN</t>
@@ -17089,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -17143,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17168,11 +16664,7 @@
           <t>18 046 03 011</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-011</t>
-        </is>
-      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>FRED WILLIAMS ESTATE</t>
@@ -17221,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -17275,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17300,11 +16792,7 @@
           <t>R6120 107</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>GW-R6120-107</t>
-        </is>
-      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>W W BUILDERS</t>
@@ -17353,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -17407,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17432,11 +16920,7 @@
           <t>18 047 23 016</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>DK-18-047-23-016</t>
-        </is>
-      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>BROWN JOHNSON</t>
@@ -17485,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17539,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17564,11 +17048,7 @@
           <t>15 058 05 035</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>DK-15-058-05-035</t>
-        </is>
-      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>LEROY HARDING 3289 BLAZING PINE KNL #A DECATUR 30034</t>
@@ -17617,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17671,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17696,11 +17176,7 @@
           <t>18 225 03 022</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>DK-18-225-03-022</t>
-        </is>
-      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>P D HOPKINS</t>
@@ -17749,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17803,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17828,11 +17304,7 @@
           <t>R6114 027</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>GW-R6114-027</t>
-        </is>
-      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>CELESTINO MACEDO-JAMES</t>
@@ -17881,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17935,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17960,11 +17432,7 @@
           <t>R5137 171</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>GW-R5137-171</t>
-        </is>
-      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>BP DIVERSIFIED ASSETS GROUP</t>
@@ -18013,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -18067,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18092,11 +17560,7 @@
           <t>16 074 08 101</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>DK-16-074-08-101</t>
-        </is>
-      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>ETHEL J MABRY ESTATE</t>
@@ -18145,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -18199,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18224,11 +17688,7 @@
           <t>R4349 085</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>GW-R4349-085</t>
-        </is>
-      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>ELITE</t>
@@ -18277,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -18331,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18356,11 +17816,7 @@
           <t>15 174 08 067</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>DK-15-174-08-067</t>
-        </is>
-      </c>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>W C ELLINGTON</t>
@@ -18409,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -18463,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18488,11 +17944,7 @@
           <t>16 009 02 005</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>DK-16-009-02-005</t>
-        </is>
-      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>ROSE BURNEY</t>
@@ -18541,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18595,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18620,11 +18072,7 @@
           <t>15 191 01 108</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>DK-15-191-01-108</t>
-        </is>
-      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>BRUCE T HANSEN</t>
@@ -18673,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18727,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18752,11 +18200,7 @@
           <t>16 169 07 061</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>DK-16-169-07-061</t>
-        </is>
-      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>TOMMIE ABBOTT</t>
@@ -18805,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18859,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-106</v>
+        <v>-107</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-141</v>
+        <v>-142</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-142</v>
+        <v>-143</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-143</v>
+        <v>-144</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-46</v>
+        <v>-45</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-46</v>
+        <v>-45</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-46</v>
+        <v>-45</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-144</v>
+        <v>-143</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-46</v>
+        <v>-45</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-46</v>
+        <v>-45</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-46</v>
+        <v>-45</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-45</v>
+        <v>-47</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-45</v>
+        <v>-47</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-45</v>
+        <v>-47</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6585,7 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PEACHTREE/SUWANEE</t>
+          <t>PEACHTREE / SUWANEE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -10425,7 +10425,7 @@
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>JERE M.</t>
+          <t>JERE M</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-143</v>
+        <v>-145</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-45</v>
+        <v>-47</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-45</v>
+        <v>-47</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -15520,14 +15520,14 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
+          <t>Individual / Estate</t>
         </is>
       </c>
       <c r="G119" t="b">
         <v>1</v>
       </c>
       <c r="H119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-45</v>
+        <v>-47</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-145</v>
+        <v>-146</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-146</v>
+        <v>-147</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-147</v>
+        <v>-148</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-113</v>
+        <v>-114</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-148</v>
+        <v>-149</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-150</v>
+        <v>-151</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-116</v>
+        <v>-117</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-151</v>
+        <v>-152</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -9575,11 +9575,11 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-117</v>
+        <v>-118</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-152</v>
+        <v>-153</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>

--- a/exports/Georgia_Surplus_Feed.xlsx
+++ b/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-118</v>
+        <v>-119</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-153</v>
+        <v>-154</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
